--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30387,6 +30387,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1306">
+      <c r="A1306" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1306" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C1306" t="n">
+        <v>0.629999995231628</v>
+      </c>
+      <c r="D1306" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="G1306" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30410,6 +30410,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1307">
+      <c r="A1307" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1307" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C1307" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>0.605000019073486</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>0.605000019073486</v>
+      </c>
+      <c r="G1307" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30433,6 +30433,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1308">
+      <c r="A1308" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1308" t="n">
+        <v>27600</v>
+      </c>
+      <c r="C1308" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="G1308" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30297,19 +30297,19 @@
     </row>
     <row r="1302">
       <c r="A1302" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1302" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="C1302" t="n">
         <v>0.589999973773956</v>
       </c>
       <c r="D1302" t="n">
-        <v>0.589999973773956</v>
+        <v>0.579999983310699</v>
       </c>
       <c r="E1302" t="n">
-        <v>0.589999973773956</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="F1302" t="n">
         <v>0.589999973773956</v>
@@ -30320,22 +30320,22 @@
     </row>
     <row r="1303">
       <c r="A1303" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1303" t="n">
-        <v>12000</v>
+        <v>400</v>
       </c>
       <c r="C1303" t="n">
-        <v>0.610000014305115</v>
+        <v>0.589999973773956</v>
       </c>
       <c r="D1303" t="n">
-        <v>0.584999978542328</v>
+        <v>0.589999973773956</v>
       </c>
       <c r="E1303" t="n">
-        <v>0.600000023841858</v>
+        <v>0.589999973773956</v>
       </c>
       <c r="F1303" t="n">
-        <v>0.600000023841858</v>
+        <v>0.589999973773956</v>
       </c>
       <c r="G1303" t="s">
         <v>7</v>
@@ -30343,22 +30343,22 @@
     </row>
     <row r="1304">
       <c r="A1304" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1304" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="C1304" t="n">
-        <v>0.629999995231628</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="D1304" t="n">
-        <v>0.610000014305115</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="E1304" t="n">
-        <v>0.610000014305115</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="F1304" t="n">
-        <v>0.629999995231628</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="G1304" t="s">
         <v>7</v>
@@ -30366,22 +30366,22 @@
     </row>
     <row r="1305">
       <c r="A1305" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1305" t="n">
-        <v>2800</v>
+        <v>2000</v>
       </c>
       <c r="C1305" t="n">
+        <v>0.629999995231628</v>
+      </c>
+      <c r="D1305" t="n">
         <v>0.610000014305115</v>
-      </c>
-      <c r="D1305" t="n">
-        <v>0.600000023841858</v>
       </c>
       <c r="E1305" t="n">
         <v>0.610000014305115</v>
       </c>
       <c r="F1305" t="n">
-        <v>0.600000023841858</v>
+        <v>0.629999995231628</v>
       </c>
       <c r="G1305" t="s">
         <v>7</v>
@@ -30389,22 +30389,22 @@
     </row>
     <row r="1306">
       <c r="A1306" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1306" t="n">
-        <v>21200</v>
+        <v>2800</v>
       </c>
       <c r="C1306" t="n">
-        <v>0.629999995231628</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="D1306" t="n">
-        <v>0.615000009536743</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="E1306" t="n">
-        <v>0.620000004768372</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="F1306" t="n">
-        <v>0.615000009536743</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="G1306" t="s">
         <v>7</v>
@@ -30412,22 +30412,22 @@
     </row>
     <row r="1307">
       <c r="A1307" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1307" t="n">
-        <v>4400</v>
+        <v>21200</v>
       </c>
       <c r="C1307" t="n">
-        <v>0.620000004768372</v>
+        <v>0.629999995231628</v>
       </c>
       <c r="D1307" t="n">
-        <v>0.605000019073486</v>
+        <v>0.615000009536743</v>
       </c>
       <c r="E1307" t="n">
         <v>0.620000004768372</v>
       </c>
       <c r="F1307" t="n">
-        <v>0.605000019073486</v>
+        <v>0.615000009536743</v>
       </c>
       <c r="G1307" t="s">
         <v>7</v>
@@ -30435,24 +30435,70 @@
     </row>
     <row r="1308">
       <c r="A1308" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1308" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C1308" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>0.605000019073486</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>0.605000019073486</v>
+      </c>
+      <c r="G1308" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="1" t="n">
         <v>46281.2916666667</v>
       </c>
-      <c r="B1308" t="n">
+      <c r="B1309" t="n">
         <v>27600</v>
       </c>
-      <c r="C1308" t="n">
+      <c r="C1309" t="n">
         <v>0.595000028610229</v>
       </c>
-      <c r="D1308" t="n">
+      <c r="D1309" t="n">
         <v>0.564999997615814</v>
       </c>
-      <c r="E1308" t="n">
+      <c r="E1309" t="n">
         <v>0.595000028610229</v>
       </c>
-      <c r="F1308" t="n">
+      <c r="F1309" t="n">
         <v>0.564999997615814</v>
       </c>
-      <c r="G1308" t="s">
+      <c r="G1309" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1310" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C1310" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="G1310" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -34539,6 +34539,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1315">
+      <c r="A1315" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1315" t="n">
+        <v>5600</v>
+      </c>
+      <c r="C1315" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G1315" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="H1315" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -34565,6 +34565,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1316">
+      <c r="A1316" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1316" t="n">
+        <v>8800</v>
+      </c>
+      <c r="C1316" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G1316" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="H1316" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -34643,6 +34643,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1319">
+      <c r="A1319" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1319" t="n">
+        <v>800</v>
+      </c>
+      <c r="C1319" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="H1319" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30725,7 +30725,9 @@
       <c r="E1320" t="n">
         <v>0.550000011920929</v>
       </c>
-      <c r="F1320"/>
+      <c r="F1320" t="n">
+        <v>0.550000011920929</v>
+      </c>
       <c r="G1320" t="s">
         <v>7</v>
       </c>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30732,6 +30732,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1321">
+      <c r="A1321" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1321" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1321" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1321" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30755,6 +30755,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1322">
+      <c r="A1322" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1322" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1322" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1322" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1323" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1323" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1323"/>
+      <c r="G1323" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30794,8 +30794,31 @@
       <c r="E1323" t="n">
         <v>0.550000011920929</v>
       </c>
-      <c r="F1323"/>
+      <c r="F1323" t="n">
+        <v>0.550000011920929</v>
+      </c>
       <c r="G1323" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1324" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1324" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1324"/>
+      <c r="G1324" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30817,8 +30817,31 @@
       <c r="E1324" t="n">
         <v>0.550000011920929</v>
       </c>
-      <c r="F1324"/>
+      <c r="F1324" t="n">
+        <v>0.550000011920929</v>
+      </c>
       <c r="G1324" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1325" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1325" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1325"/>
+      <c r="G1325" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30840,8 +30840,31 @@
       <c r="E1325" t="n">
         <v>0.550000011920929</v>
       </c>
-      <c r="F1325"/>
+      <c r="F1325" t="n">
+        <v>0.550000011920929</v>
+      </c>
       <c r="G1325" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1326" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1326" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1326"/>
+      <c r="G1326" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -30870,6 +30870,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1327">
+      <c r="A1327" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1327" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C1327" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G1327" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -34929,6 +34929,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1330">
+      <c r="A1330" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1330" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C1330" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="H1330" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -38977,6 +38977,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1332">
+      <c r="A1332" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1332" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1332" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="H1332" t="n">
+        <v>43600</v>
+      </c>
+      <c r="I1332" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1333" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1333" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="G1333" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>72000</v>
+      </c>
+      <c r="I1333" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -39035,6 +39035,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1334">
+      <c r="A1334" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1334" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1334" t="n">
+        <v>0.535000026226044</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>0.535000026226044</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>6800</v>
+      </c>
+      <c r="I1334" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -39064,6 +39064,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1335">
+      <c r="A1335" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1335" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="H1335" t="n">
+        <v>400</v>
+      </c>
+      <c r="I1335" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -39093,6 +39093,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1336">
+      <c r="A1336" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1336" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1336" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1336" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="H1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1336" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1337" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1337" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G1337" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H1337" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I1337" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -39151,6 +39151,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1338">
+      <c r="A1338" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1338" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1338" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G1338" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H1338" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1338" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1339" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1339" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G1339" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H1339" t="n">
+        <v>400</v>
+      </c>
+      <c r="I1339" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GCOM.MI.xlsx
+++ b/data/GCOM.MI.xlsx
@@ -39209,6 +39209,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1340">
+      <c r="A1340" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1340" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1340" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G1340" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H1340" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I1340" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
